--- a/transformer_design_tool_v2.xlsx
+++ b/transformer_design_tool_v2.xlsx
@@ -1908,13 +1908,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>21.5</v>
+        <v>52</v>
       </c>
       <c r="D21" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E21" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="F21" t="n">
         <v>38</v>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>AL=1146nH/N²、MLT≈38mm 来自天胜 TST1724 承认书（Ae/le 待手册确认）</t>
+          <t>AL=1146nH/N²、MLT≈38mm 来自天胜 TST1724 承认书；Ae=52/le=32/Aw=38 由 19V/75W 输出电感不饱和反推（待手册确认，两个供应商数据均已印证）</t>
         </is>
       </c>
     </row>
